--- a/questionnaire_templates/039_pre_exercise_health_questionnaire--questionnaire_templates.xlsx
+++ b/questionnaire_templates/039_pre_exercise_health_questionnaire--questionnaire_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -987,8 +987,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="37" customWidth="1" min="2" max="2"/>
-    <col width="37" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1016,12 +1016,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Excellent'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -1033,12 +1033,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1050,12 +1050,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'average'}</t>
+          <t>average</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Average'}</t>
+          <t>Average</t>
         </is>
       </c>
     </row>
@@ -1067,12 +1067,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'bad'}</t>
+          <t>bad</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Bad'}</t>
+          <t>Bad</t>
         </is>
       </c>
     </row>
@@ -1084,12 +1084,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -1101,12 +1101,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'occasionally'}</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Occasionally'}</t>
+          <t>Occasionally</t>
         </is>
       </c>
     </row>
@@ -1118,12 +1118,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'frequently'}</t>
+          <t>frequently</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Frequently'}</t>
+          <t>Frequently</t>
         </is>
       </c>
     </row>
@@ -1135,12 +1135,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'often'}</t>
+          <t>often</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Often'}</t>
+          <t>Often</t>
         </is>
       </c>
     </row>
@@ -1152,12 +1152,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'heart_conditions'}</t>
+          <t>heart_conditions</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Heart Conditions'}</t>
+          <t>Heart Conditions</t>
         </is>
       </c>
     </row>
@@ -1169,12 +1169,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'diabetes'}</t>
+          <t>diabetes</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Diabetes'}</t>
+          <t>Diabetes</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1203,12 +1203,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_none}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': None}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1220,12 +1220,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_none}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': None}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1237,12 +1237,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1254,12 +1254,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'heart_surgery'}</t>
+          <t>heart_surgery</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Heart Surgery'}</t>
+          <t>Heart Surgery</t>
         </is>
       </c>
     </row>
@@ -1271,12 +1271,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'more_than_6_months_ago'}</t>
+          <t>more_than_6_months_ago</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'More than 6 months ago'}</t>
+          <t>More than 6 months ago</t>
         </is>
       </c>
     </row>
@@ -1305,12 +1305,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'less_than_6_months_ago'}</t>
+          <t>less_than_6_months_ago</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Less than 6 months ago'}</t>
+          <t>Less than 6 months ago</t>
         </is>
       </c>
     </row>
@@ -1322,12 +1322,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'1-2_months_ago'}</t>
+          <t>1-2_months_ago</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': '1-2 months ago'}</t>
+          <t>1-2 months ago</t>
         </is>
       </c>
     </row>
@@ -1339,12 +1339,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'less_than_1_month_ago'}</t>
+          <t>less_than_1_month_ago</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Less than 1 month ago'}</t>
+          <t>Less than 1 month ago</t>
         </is>
       </c>
     </row>
@@ -1356,12 +1356,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'heart_conditions'}</t>
+          <t>heart_conditions</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Heart Conditions'}</t>
+          <t>Heart Conditions</t>
         </is>
       </c>
     </row>
@@ -1373,12 +1373,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'high_blood_pressure'}</t>
+          <t>high_blood_pressure</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'High Blood Pressure'}</t>
+          <t>High Blood Pressure</t>
         </is>
       </c>
     </row>
@@ -1390,12 +1390,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1407,12 +1407,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1424,12 +1424,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'knee_problems'}</t>
+          <t>knee_problems</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'Knee Problems'}</t>
+          <t>Knee Problems</t>
         </is>
       </c>
     </row>
@@ -1441,12 +1441,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'back_problems'}</t>
+          <t>back_problems</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 'Back Problems'}</t>
+          <t>Back Problems</t>
         </is>
       </c>
     </row>
@@ -1458,12 +1458,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1475,12 +1475,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
